--- a/artfynd/A 50989-2023 artfynd.xlsx
+++ b/artfynd/A 50989-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50989-2023 artfynd.xlsx
+++ b/artfynd/A 50989-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112513401</v>
+        <v>112513399</v>
       </c>
       <c r="B2" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,7 +722,7 @@
         <v>510990</v>
       </c>
       <c r="R2" t="n">
-        <v>6639277</v>
+        <v>6639276</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112513399</v>
+        <v>112513401</v>
       </c>
       <c r="B3" t="n">
-        <v>90907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,7 +833,7 @@
         <v>510990</v>
       </c>
       <c r="R3" t="n">
-        <v>6639277</v>
+        <v>6639276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,12 +900,7 @@
         <v>112513402</v>
       </c>
       <c r="B4" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,12 +917,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510991</v>
+        <v>510992</v>
       </c>
       <c r="R4" t="n">
         <v>6639254</v>

--- a/artfynd/A 50989-2023 artfynd.xlsx
+++ b/artfynd/A 50989-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>